--- a/outputs_xlsx_solution/prog-loop.4-wide-NB-1.xlsx
+++ b/outputs_xlsx_solution/prog-loop.4-wide-NB-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -609,10 +615,10 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -632,22 +638,22 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -670,10 +676,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -693,16 +699,16 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
         <v>14</v>
@@ -737,10 +743,10 @@
         <v>14</v>
       </c>
       <c r="M6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +766,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N8" t="s">
         <v>14</v>
@@ -801,19 +807,19 @@
         <v>14</v>
       </c>
       <c r="Q8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -833,16 +839,16 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U9" t="s">
         <v>14</v>
       </c>
       <c r="V9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -853,7 +859,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -865,13 +871,13 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -882,7 +888,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -891,19 +897,19 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -914,7 +920,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -923,16 +929,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -952,16 +958,16 @@
         <v>9</v>
       </c>
       <c r="M13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N13" t="s">
         <v>14</v>
       </c>
       <c r="O13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -981,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O14" t="s">
         <v>14</v>
@@ -996,19 +1002,19 @@
         <v>14</v>
       </c>
       <c r="S14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1028,16 +1034,19 @@
         <v>9</v>
       </c>
       <c r="M15" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" t="s">
         <v>15</v>
       </c>
       <c r="O15" t="s">
         <v>14</v>
       </c>
       <c r="P15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1057,7 +1066,7 @@
         <v>9</v>
       </c>
       <c r="M16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V16" t="s">
         <v>14</v>
@@ -1069,13 +1078,13 @@
         <v>14</v>
       </c>
       <c r="Y16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -1095,16 +1104,16 @@
         <v>9</v>
       </c>
       <c r="N17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="s">
         <v>14</v>
       </c>
       <c r="AB17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1115,7 +1124,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L18" t="s">
         <v>5</v>
@@ -1124,19 +1133,19 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" t="s">
         <v>14</v>
       </c>
       <c r="P18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1147,7 +1156,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" t="s">
         <v>5</v>
@@ -1156,22 +1165,25 @@
         <v>9</v>
       </c>
       <c r="N19" t="s">
+        <v>16</v>
+      </c>
+      <c r="O19" t="s">
         <v>15</v>
       </c>
       <c r="P19" t="s">
         <v>14</v>
       </c>
       <c r="Q19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1182,7 +1194,7 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" t="s">
         <v>5</v>
@@ -1191,16 +1203,16 @@
         <v>9</v>
       </c>
       <c r="N20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="s">
         <v>14</v>
       </c>
       <c r="R20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1220,16 +1232,16 @@
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" t="s">
         <v>14</v>
       </c>
       <c r="R21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1249,8 +1261,20 @@
         <v>9</v>
       </c>
       <c r="O22" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" t="s">
         <v>15</v>
       </c>
+      <c r="S22" t="s">
+        <v>15</v>
+      </c>
+      <c r="T22" t="s">
+        <v>15</v>
+      </c>
+      <c r="U22" t="s">
+        <v>15</v>
+      </c>
       <c r="V22" t="s">
         <v>14</v>
       </c>
@@ -1264,16 +1288,16 @@
         <v>14</v>
       </c>
       <c r="Z22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1293,19 +1317,19 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S23" t="s">
         <v>14</v>
       </c>
       <c r="T23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1325,22 +1349,22 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AB24" t="s">
         <v>14</v>
@@ -1352,7 +1376,7 @@
         <v>14</v>
       </c>
       <c r="AE24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1372,19 +1396,19 @@
         <v>9</v>
       </c>
       <c r="U25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="s">
         <v>14</v>
       </c>
       <c r="AF25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1395,7 +1419,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N26" t="s">
         <v>5</v>
@@ -1404,16 +1428,16 @@
         <v>9</v>
       </c>
       <c r="W26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
       </c>
       <c r="Y26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1424,7 +1448,7 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N27" t="s">
         <v>5</v>
@@ -1433,16 +1457,19 @@
         <v>9</v>
       </c>
       <c r="W27" t="s">
+        <v>16</v>
+      </c>
+      <c r="X27" t="s">
         <v>15</v>
       </c>
       <c r="Y27" t="s">
         <v>14</v>
       </c>
       <c r="Z27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1453,7 +1480,7 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N28" t="s">
         <v>5</v>
@@ -1462,21 +1489,21 @@
         <v>9</v>
       </c>
       <c r="W28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y28" t="s">
         <v>14</v>
       </c>
       <c r="Z28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -1484,7 +1511,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -1492,15 +1519,15 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
@@ -1508,39 +1535,55 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
